--- a/deepseek-excel-assistant-sideload.xlsx
+++ b/deepseek-excel-assistant-sideload.xlsx
@@ -1519,7 +1519,7 @@
 
 <file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
 <we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{7c1e9a24-5d3f-4b8e-9c2a-0f6d1b4e8a5c}">
-  <we:reference id="7c1e9a24-5d3f-4b8e-9c2a-0f6d1b4e8a5c" version="1.0.39.0" store="developer" storeType="Registry"/>
+  <we:reference id="7c1e9a24-5d3f-4b8e-9c2a-0f6d1b4e8a5c" version="1.0.40.0" store="developer" storeType="Registry"/>
   <we:alternateReferences/>
   <we:properties/>
   <we:bindings/>
